--- a/DateBase/orders/Nha Thu_2026-9-16.xlsx
+++ b/DateBase/orders/Nha Thu_2026-9-16.xlsx
@@ -894,6 +894,9 @@
       <c r="G2" t="str">
         <v>010101025101522252021216320535253010521203151191111251785555205301051151215</v>
       </c>
+      <c r="H2" t="str">
+        <v>CNY</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
